--- a/기타/11.13 2차구매목록.xlsx
+++ b/기타/11.13 2차구매목록.xlsx
@@ -1,42 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dbstj\OneDrive\바탕 화면\main_project\SynchroBots_DOC\기타\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\SynchroBots\SynchroBots_DOC\기타\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FAC762A-EA6F-4A05-8C43-8C576EC11B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F1F497-39E1-4765-BDDD-4DE22AC817AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{343932E5-CCDF-4074-96BC-E269E36EA69C}"/>
+    <workbookView xWindow="3828" yWindow="1416" windowWidth="18000" windowHeight="9216" xr2:uid="{343932E5-CCDF-4074-96BC-E269E36EA69C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>구매요청 목록</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -67,25 +56,47 @@
     <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=1030079&amp;recmYn=N</t>
   </si>
   <si>
+    <t>가죽시트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8590971632?itemId=24909064041&amp;vendorItemId=92048503820&amp;q=60%ED%94%84%EB%A0%88%EC%9E%84+%EC%9B%B9%EC%BA%A0&amp;searchId=6953b0036113572&amp;sourceType=search&amp;itemsCount=36&amp;searchRank=2&amp;rank=2&amp;traceId=mhsxejk2</t>
+  </si>
+  <si>
+    <t>너츠 60fps 스트리밍 웹캠 SC-100</t>
+  </si>
+  <si>
+    <t>쿠팡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가격(원)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=1035663&amp;recmYn=N</t>
-  </si>
-  <si>
-    <t>가죽시트</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.coupang.com/vp/products/8590971632?itemId=24909064041&amp;vendorItemId=92048503820&amp;q=60%ED%94%84%EB%A0%88%EC%9E%84+%EC%9B%B9%EC%BA%A0&amp;searchId=6953b0036113572&amp;sourceType=search&amp;itemsCount=36&amp;searchRank=2&amp;rank=2&amp;traceId=mhsxejk2</t>
-  </si>
-  <si>
-    <t>너츠 60fps 스트리밍 웹캠 SC-100</t>
-  </si>
-  <si>
-    <t>쿠팡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가격(원)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>헤드렌턴 1,200mA</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=1048547&amp;recmYn=N</t>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8698545519?itemId=12918597038&amp;vendorItemId=80183246703&amp;q=%ED%95%98%EC%9D%B4%EB%9D%BC%EC%9D%B4%ED%8A%B8+%EC%A1%B0%EB%AA%85&amp;searchId=29f59d5c3577489&amp;sourceType=search&amp;itemsCount=36&amp;searchRank=5&amp;rank=5&amp;traceId=mhu7yvlc</t>
+  </si>
+  <si>
+    <t>조명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LED 하이라이트</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.coupang.com/vp/products/8492126035?itemId=182439054&amp;vendorItemId=3434578156&amp;q=%ED%95%98%EC%9D%B4%EB%9D%BC%EC%9D%B4%ED%8A%B8+%EC%A1%B0%EB%AA%85&amp;searchId=29f59d5c3577489&amp;sourceType=search&amp;itemsCount=36&amp;searchRank=2&amp;rank=2&amp;traceId=mhu81609</t>
   </si>
 </sst>
 </file>
@@ -95,7 +106,7 @@
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,6 +130,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -137,15 +157,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -158,10 +181,14 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -473,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0286A5A-816F-482B-ADB4-3C79FD5C7800}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="30.09765625" bestFit="1" customWidth="1"/>
@@ -491,7 +518,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -524,31 +551,81 @@
       <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" t="s">
-        <v>8</v>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1">
         <v>78900</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1">
+        <v>3000</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1">
+        <v>7980</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1">
+        <v>7000</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D5" r:id="rId1" xr:uid="{E01FBECF-9924-4AB1-9CD6-69EA6507F46F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>